--- a/01_Thermal/B_results/Single_Fan_GP/single_fan_gp_summary.xlsx
+++ b/01_Thermal/B_results/Single_Fan_GP/single_fan_gp_summary.xlsx
@@ -472,26 +472,26 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04888559229606983</v>
+        <v>0.06354367205669519</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1488947044763873</v>
+        <v>0.2177451183831809</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9373581861506823</v>
+        <v>0.8660315060494127</v>
       </c>
       <c r="E2" t="n">
         <v>1365</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-323.6571055089172</v>
+        <v>-1080.737637787924</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.29**2 * RBF(length_scale=[0.161, 0.247]) + WhiteKernel(noise_level=0.0254)</t>
+          <t>0.892**2 * RBF(length_scale=[0.0139, 0.0264, 5.59]) + WhiteKernel(noise_level=0.121)</t>
         </is>
       </c>
     </row>
@@ -562,16 +562,16 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03722618755144055</v>
+        <v>0.09169913356318102</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08945432812682572</v>
+        <v>0.3147247713177155</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9848266328504215</v>
+        <v>0.8121803168577898</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1075416023883879</v>
+        <v>0.2342810074888955</v>
       </c>
     </row>
     <row r="3">
@@ -590,16 +590,16 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03593966486519642</v>
+        <v>0.07249325707249819</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1050543145363409</v>
+        <v>0.2266544358990011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9772763946411375</v>
+        <v>0.8942262509557737</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1066133844133028</v>
+        <v>0.2306335642249533</v>
       </c>
     </row>
     <row r="4">
@@ -618,16 +618,16 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06264613746429877</v>
+        <v>0.08554718648263916</v>
       </c>
       <c r="F4" t="n">
-        <v>0.193826211313661</v>
+        <v>0.3188003483487614</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9131110801052289</v>
+        <v>0.7649409591980411</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1062475443796069</v>
+        <v>0.2278131799942498</v>
       </c>
     </row>
     <row r="5">
@@ -646,16 +646,16 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05941399538749544</v>
+        <v>0.05235434558014433</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1834390001811531</v>
+        <v>0.175770116038652</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9034019301021698</v>
+        <v>0.9113098930597252</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1039695584946864</v>
+        <v>0.2249757529328979</v>
       </c>
     </row>
     <row r="6">
@@ -674,16 +674,16 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05814513501454485</v>
+        <v>0.05937614083991262</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1935207102413423</v>
+        <v>0.1639145795430342</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8418139735186675</v>
+        <v>0.8865124065887986</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1051399779274311</v>
+        <v>0.2248856665633595</v>
       </c>
     </row>
     <row r="7">
@@ -702,16 +702,16 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04808430626147474</v>
+        <v>0.04077432006516223</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1411273987860422</v>
+        <v>0.1165936320615116</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9236976784182489</v>
+        <v>0.9479207476094645</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1120957694971397</v>
+        <v>0.2321711492895556</v>
       </c>
     </row>
     <row r="8">
@@ -730,16 +730,16 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04074371952803803</v>
+        <v>0.04256132079332869</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08696706482545914</v>
+        <v>0.09206400404424032</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9590601259471067</v>
+        <v>0.9541207198209124</v>
       </c>
       <c r="H8" t="n">
-        <v>0.10489921514597</v>
+        <v>0.2509213252559943</v>
       </c>
     </row>
   </sheetData>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.29**2 * RBF(length_scale=[0.161, 0.247]) + WhiteKernel(noise_level=0.0254)</t>
+          <t>0.892**2 * RBF(length_scale=[0.0139, 0.0264, 5.59]) + WhiteKernel(noise_level=0.121)</t>
         </is>
       </c>
     </row>

--- a/01_Thermal/B_results/Single_Fan_GP/single_fan_gp_summary.xlsx
+++ b/01_Thermal/B_results/Single_Fan_GP/single_fan_gp_summary.xlsx
@@ -10,6 +10,7 @@
     <sheet name="overall_metrics" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="per_sheet_metrics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="hyperparameters" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="single_fan_gp_analysis" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,25 +444,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>sae_mps</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sse_mps2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>wrmse_mps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>r2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_samples</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>use_radial_features</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>log_marginal_likelihood</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>kernel</t>
         </is>
@@ -472,26 +488,35 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06354367205669519</v>
+        <v>0.06686371167524949</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2177451183831809</v>
+        <v>0.2319093134254427</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8660315060494127</v>
+        <v>91.26896643671554</v>
       </c>
       <c r="E2" t="n">
+        <v>73.4123339769732</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1731110873539931</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8480354806684861</v>
+      </c>
+      <c r="H2" t="n">
         <v>1365</v>
       </c>
-      <c r="F2" t="b">
+      <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>-1080.737637787924</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.892**2 * RBF(length_scale=[0.0139, 0.0264, 5.59]) + WhiteKernel(noise_level=0.121)</t>
+      <c r="J2" t="n">
+        <v>-1042.675284264143</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.744**2 * RBF(length_scale=[0.117, 0.194, 6.17]) + WhiteKernel(noise_level=0.132)</t>
         </is>
       </c>
     </row>
@@ -506,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,10 +562,25 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>sae_mps</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sse_mps2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>wrmse_mps</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>r2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mean_pred_std_mps</t>
         </is>
@@ -562,16 +602,25 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09169913356318102</v>
+        <v>0.102216779809836</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3147247713177155</v>
+        <v>0.3615243603878376</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8121803168577898</v>
+        <v>19.93227206291802</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2342810074888955</v>
+        <v>25.48647331499784</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4574212170103216</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7521697111277293</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2393412891192192</v>
       </c>
     </row>
     <row r="3">
@@ -590,16 +639,25 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07249325707249819</v>
+        <v>0.08224205377155676</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2266544358990011</v>
+        <v>0.2674208096681707</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8942262509557737</v>
+        <v>16.03720048545357</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2306335642249533</v>
+        <v>13.9452084414981</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1373566017815918</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8527552394084337</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.236927722826763</v>
       </c>
     </row>
     <row r="4">
@@ -618,16 +676,25 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08554718648263916</v>
+        <v>0.08184892964484289</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3188003483487614</v>
+        <v>0.2993083124036229</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7649409591980411</v>
+        <v>15.96054128074436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2278131799942498</v>
+        <v>17.46916584541142</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3268042616335176</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7928061112676772</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2350496411120093</v>
       </c>
     </row>
     <row r="5">
@@ -646,16 +713,25 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05235434558014433</v>
+        <v>0.05095226325330279</v>
       </c>
       <c r="F5" t="n">
-        <v>0.175770116038652</v>
+        <v>0.1709855573988896</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9113098930597252</v>
+        <v>9.935691334394043</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2249757529328979</v>
+        <v>5.70103186360675</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.06534230898359385</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9160725637845269</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2331334311209098</v>
       </c>
     </row>
     <row r="6">
@@ -674,16 +750,25 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05937614083991262</v>
+        <v>0.05940408030604913</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1639145795430342</v>
+        <v>0.1627721412884576</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8865124065887986</v>
+        <v>11.58379565967958</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2248856665633595</v>
+        <v>5.166480146027773</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.102848838829091</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8880888465568575</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2330135919763815</v>
       </c>
     </row>
     <row r="7">
@@ -702,16 +787,25 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04077432006516223</v>
+        <v>0.04174780615965168</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1165936320615116</v>
+        <v>0.1251469392496207</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9479207476094645</v>
+        <v>8.140822201132078</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2321711492895556</v>
+        <v>3.054042498691909</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1180027175481368</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9399994069194304</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2378555304843354</v>
       </c>
     </row>
     <row r="8">
@@ -730,16 +824,25 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04256132079332869</v>
+        <v>0.0496340687815072</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09206400404424032</v>
+        <v>0.1152462662332923</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9541207198209124</v>
+        <v>9.678643412393903</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2509213252559943</v>
+        <v>2.589931866739402</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.06497669868203118</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9281063381302419</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2506224604280322</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +948,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="8">
@@ -858,7 +961,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="9">
@@ -871,7 +974,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -898,8 +1001,286 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.892**2 * RBF(length_scale=[0.0139, 0.0264, 5.59]) + WhiteKernel(noise_level=0.121)</t>
-        </is>
+          <t>0.744**2 * RBF(length_scale=[0.117, 0.194, 6.17]) + WhiteKernel(noise_level=0.132)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>z_m</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_samples</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>accumulate_SAE_mps</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SSE_mps2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_RMSE_mps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_SSE_term</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>weight_sum_term</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>z020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>195</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.93227206291802</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.48647331499784</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4574212170103216</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2511.573847332075</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12003.65050354092</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>z035</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C3" t="n">
+        <v>195</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16.03720048545357</v>
+      </c>
+      <c r="E3" t="n">
+        <v>13.9452084414981</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1373566017815918</v>
+      </c>
+      <c r="G3" t="n">
+        <v>184.9552443677061</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9803.193489796933</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>z050</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>195</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.96054128074436</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.46916584541142</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3268042616335176</v>
+      </c>
+      <c r="G4" t="n">
+        <v>970.9247904152544</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9090.968804657296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>z075</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>195</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.935691334394043</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.70103186360675</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06534230898359385</v>
+      </c>
+      <c r="G5" t="n">
+        <v>305.8787993476448</v>
+      </c>
+      <c r="H5" t="n">
+        <v>71640.79933933762</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>z110</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>195</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11.58379565967958</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.166480146027773</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.102848838829091</v>
+      </c>
+      <c r="G6" t="n">
+        <v>169.73978431334</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16046.66774128612</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>z160</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>195</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.140822201132078</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.054042498691909</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1180027175481368</v>
+      </c>
+      <c r="G7" t="n">
+        <v>75.2495531803529</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5404.056829595331</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>z220</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>195</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.678643412393903</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.589931866739402</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06497669868203118</v>
+      </c>
+      <c r="G8" t="n">
+        <v>82.43358210172131</v>
+      </c>
+      <c r="H8" t="n">
+        <v>19524.90314262348</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D9" t="n">
+        <v>91.26896643671554</v>
+      </c>
+      <c r="E9" t="n">
+        <v>73.4123339769732</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1731110873539931</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4300.755601058096</v>
+      </c>
+      <c r="H9" t="n">
+        <v>143514.2398508377</v>
       </c>
     </row>
   </sheetData>
